--- a/output/pdf_financials_xlsx/MGMA.xlsx
+++ b/output/pdf_financials_xlsx/MGMA.xlsx
@@ -3169,16 +3169,16 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>7.341858</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>8.229425000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.430469</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>8.442791</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -5670,7 +5670,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -6188,7 +6192,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -6712,7 +6720,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MGMA.xlsx
+++ b/output/pdf_financials_xlsx/MGMA.xlsx
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.040108</v>
+        <v>1.333855</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.8089769999999999</v>
+        <v>1.462881</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.934728</v>
+        <v>1.94073</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.393741</v>
+        <v>0.824743</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.246071</v>
+        <v>0.755965</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.028364</v>
+        <v>0.188551</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.647065</v>
+        <v>2.115419</v>
       </c>
     </row>
     <row r="11">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1.040108</v>
+        <v>-1.333855</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.8089769999999999</v>
+        <v>-1.462881</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.934728</v>
+        <v>-1.94073</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.393741</v>
+        <v>-0.824743</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.246071</v>
+        <v>-0.755965</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.028364</v>
+        <v>-0.188551</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.647065</v>
+        <v>-2.115419</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00475</v>
       </c>
     </row>
     <row r="13">
@@ -1195,7 +1195,7 @@
         <v>0.178653</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.092142</v>
+        <v>-2.096892</v>
       </c>
     </row>
     <row r="28">
@@ -1251,7 +1251,7 @@
         <v>0.178653</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.092142</v>
+        <v>-2.096892</v>
       </c>
     </row>
     <row r="30">
@@ -1385,22 +1385,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.025223</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.16502</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.062745</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001045</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.027716</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.620474</v>
       </c>
     </row>
     <row r="35">
@@ -1445,22 +1445,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.025223</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.16502</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.062745</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001045</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.027716</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.620474</v>
       </c>
     </row>
     <row r="37">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.08414099999999999</v>
+        <v>0.058918</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.216796</v>
+        <v>0.051776</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -1817,10 +1817,10 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.032698664</v>
+        <v>0.004982664</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.668492</v>
+        <v>0.048018</v>
       </c>
     </row>
     <row r="49">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -16471,14 +16471,14 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E238" s="5" t="n">
-        <v>-1.333855</v>
+        <v>1.333855</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>-1.462881</v>
+        <v>1.462881</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E239" s="5" t="n">

--- a/output/pdf_financials_xlsx/MGMA.xlsx
+++ b/output/pdf_financials_xlsx/MGMA.xlsx
@@ -592,22 +592,22 @@
         <v>1.040108</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.8089769999999999</v>
+        <v>0.816487</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.934728</v>
+        <v>0.95213</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.393741</v>
+        <v>0.403954</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.246071</v>
+        <v>0.261955</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.028364</v>
+        <v>0.03253</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.402437</v>
+        <v>0.439022</v>
       </c>
     </row>
     <row r="8">
@@ -3422,10 +3422,10 @@
         <v>0.009388000000000001</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.001757</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.039785</v>
       </c>
     </row>
     <row r="102">
@@ -3562,10 +3562,10 @@
         <v>0.445987</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.170019</v>
+        <v>-0.168262</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.010514</v>
+        <v>-0.050299</v>
       </c>
     </row>
     <row r="107">
@@ -6932,7 +6932,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -7173,7 +7177,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -11031,7 +11039,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
